--- a/1.xlsx
+++ b/1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24000" windowHeight="10755"/>
+    <workbookView windowWidth="24000" windowHeight="11055"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1152,10 +1152,10 @@
         <v>5</v>
       </c>
       <c r="C4" s="4">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D4" s="4">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1164,10 +1164,10 @@
         <v>6</v>
       </c>
       <c r="C5" s="4">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D5" s="4">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1176,10 +1176,10 @@
         <v>7</v>
       </c>
       <c r="C6" s="4">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D6" s="4">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1188,10 +1188,10 @@
         <v>8</v>
       </c>
       <c r="C7" s="4">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D7" s="4">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1202,10 +1202,10 @@
         <v>10</v>
       </c>
       <c r="C8" s="4">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D8" s="4">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1214,10 +1214,10 @@
         <v>11</v>
       </c>
       <c r="C9" s="4">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D9" s="4">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1226,10 +1226,10 @@
         <v>12</v>
       </c>
       <c r="C10" s="4">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D10" s="4">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1240,10 +1240,10 @@
         <v>14</v>
       </c>
       <c r="C11" s="4">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D11" s="4">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1252,10 +1252,10 @@
         <v>15</v>
       </c>
       <c r="C12" s="4">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D12" s="4">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1264,10 +1264,10 @@
         <v>16</v>
       </c>
       <c r="C13" s="4">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D13" s="4">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1276,10 +1276,10 @@
         <v>17</v>
       </c>
       <c r="C14" s="4">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D14" s="4">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1288,10 +1288,10 @@
         <v>18</v>
       </c>
       <c r="C15" s="4">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D15" s="4">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1300,10 +1300,10 @@
         <v>19</v>
       </c>
       <c r="C16" s="4">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D16" s="4">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1322,7 +1322,7 @@
         <v>23</v>
       </c>
       <c r="C19" s="4">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1331,7 +1331,7 @@
         <v>24</v>
       </c>
       <c r="C20" s="4">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1340,7 +1340,7 @@
         <v>25</v>
       </c>
       <c r="C21" s="4">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1351,7 +1351,7 @@
         <v>23</v>
       </c>
       <c r="C22" s="4">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1360,7 +1360,7 @@
         <v>24</v>
       </c>
       <c r="C23" s="4">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1369,7 +1369,7 @@
         <v>25</v>
       </c>
       <c r="C24" s="4">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1380,7 +1380,7 @@
         <v>23</v>
       </c>
       <c r="C25" s="4">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1389,7 +1389,7 @@
         <v>24</v>
       </c>
       <c r="C26" s="4">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1398,7 +1398,7 @@
         <v>25</v>
       </c>
       <c r="C27" s="4">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1409,7 +1409,7 @@
         <v>23</v>
       </c>
       <c r="C28" s="4">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1418,7 +1418,7 @@
         <v>24</v>
       </c>
       <c r="C29" s="4">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1427,7 +1427,7 @@
         <v>25</v>
       </c>
       <c r="C30" s="4">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1438,7 +1438,7 @@
         <v>23</v>
       </c>
       <c r="C31" s="4">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1447,7 +1447,7 @@
         <v>24</v>
       </c>
       <c r="C32" s="4">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1456,7 +1456,7 @@
         <v>25</v>
       </c>
       <c r="C33" s="4">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
